--- a/translations/translation_eng.xlsx
+++ b/translations/translation_eng.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pcadmin\Documents\dok\TARU\PROJEKTID\EEGManyLabs\Task\spotlight_replication\translations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364BFF60-3C09-4B07-983B-99E1A250580F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA33E7C5-70B9-49D8-B360-3C2353ACAFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>key</t>
   </si>
@@ -65,9 +65,6 @@
     <t>right_translation</t>
   </si>
   <si>
-    <t>Following are the experimental trials \n\n Press "space" to begin…</t>
-  </si>
-  <si>
     <t xml:space="preserve">Please attend locations: </t>
   </si>
   <si>
@@ -87,11 +84,6 @@
   </si>
   <si>
     <t>general_intro_2</t>
-  </si>
-  <si>
-    <t>Task Overview:\n\n
-In this experiment, you will see four white squares displayed on the screen. Your task is to focus your attention on two of these squares while ignoring the others. Throughout the trials, two objects will appear on either side of a central fixation cross. Your goal is to press the spacebar whenever the number 8 appears simultaneously in both of the squares you are attending to.\n\n
-It is important to keep your eyes fixed on the central fixation cross during stimulus presentation, even if it’s tempting to look directly at the targets in the periphery.</t>
   </si>
   <si>
     <t>general_intro_3</t>
@@ -114,27 +106,66 @@
     <t>calib_text</t>
   </si>
   <si>
-    <t>Welcome, and thank you for volunteering to participate in our experiment!\n\n</t>
-  </si>
-  <si>
     <t>general_intro_4</t>
   </si>
   <si>
     <t>Please fixate on the dot below...</t>
   </si>
   <si>
-    <t>You will briefly see eye-movement calibration screens before the practice trials and occasionally throughout the experiment. Simply look at the dot when it appears and follow it with your eyes as it changes position. Please try to keep your head still and avoid blinking when possible.\n\nPress "space" to begin with the practice…</t>
-  </si>
-  <si>
-    <t>Before starting the main experiment, you will have the opportunity to practice during 4 shorter blocks. These practice blocks are designed to help you get familiar with the task.</t>
-  </si>
-  <si>
     <t>general_intro_5</t>
   </si>
   <si>
-    <t>During practice trials:\n
-- A feedback tone will play whenever you correctly press the spacebar in response to a pair of eights appearing at the attended locations.
+    <t>feedback_on_text</t>
+  </si>
+  <si>
+    <t>feedback_off_text</t>
+  </si>
+  <si>
+    <t>Sound feedback: ON</t>
+  </si>
+  <si>
+    <t>Sound feedback: OFF</t>
+  </si>
+  <si>
+    <t>slow_text</t>
+  </si>
+  <si>
+    <t>Number of trials to be slowed down:</t>
+  </si>
+  <si>
+    <t>Welcome back!\n\nIn this session, you will first complete a brief training, followed by a series of experimental trials. The entire session will take approximately 60 minutes.</t>
+  </si>
+  <si>
+    <t>Following are the experimental trials.\n\nPlease note that you will not receive feedback during these trials.\n\n Press spacebar to begin…</t>
+  </si>
+  <si>
+    <t>pairs_sound_on_text</t>
+  </si>
+  <si>
+    <t>Pairs sound: ON</t>
+  </si>
+  <si>
+    <t>pairs_sound_off_text</t>
+  </si>
+  <si>
+    <t>Pairs sound: OFF</t>
+  </si>
+  <si>
+    <t>Reminder: Task Overview\n\n
+In this experiment, you will see four white squares displayed on the screen. Your task is to focus your attention on two of these squares while ignoring the others. Throughout the trials, two objects will appear on either side of a central fixation cross. Your goal is to press the spacebar whenever the number 8 appears simultaneously in both of the squares you are attending to.\n\n
+It is important to keep your eyes fixed on the central fixation cross during stimulus presentation, even if it’s tempting to look directly at the targets in the periphery.</t>
+  </si>
+  <si>
+    <t>You will briefly see eye-movement calibration screens before the practice trials and occasionally throughout the experiment. Simply look at the dot when it appears and follow it with your eyes as it changes position. Please try to keep your head still and avoid blinking when possible.\n\nPress spacebar to begin with the practice…</t>
+  </si>
+  <si>
+    <t>The following are practice trials. \n\nPress spacebar to continue…</t>
+  </si>
+  <si>
+    <t>Similarly to the practice session that you participated in earlier:\n
+- On first half of the training trials, a feedback tone will play whenever you correctly press the spacebar in response to a pair of eights appearing at the attended locations.
 -  To facilitate training, an additional lower-pitched tone will play whenever a pair appears, but only during the first half of the block (before the hand switch).
+- A few of the initial trials in each block will be presented at a slower pace.
 - You are encouraged to ask the experimenter any questions either now or during the practice trials.</t>
   </si>
 </sst>
@@ -178,7 +209,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normaallaad" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -456,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.5703125" customWidth="1"/>
@@ -468,47 +499,47 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="164.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -516,7 +547,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -524,7 +555,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -532,7 +563,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -540,15 +571,15 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -556,7 +587,7 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -564,7 +595,7 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -572,15 +603,55 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
         <v>22</v>
       </c>
-      <c r="B15" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/translations/translation_eng.xlsx
+++ b/translations/translation_eng.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pcadmin\Documents\dok\TARU\PROJEKTID\EEGManyLabs\Task\spotlight_replication\translations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA33E7C5-70B9-49D8-B360-3C2353ACAFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073717EB-DC5F-49BE-A1AE-484441268C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,7 +165,6 @@
     <t>Similarly to the practice session that you participated in earlier:\n
 - On first half of the training trials, a feedback tone will play whenever you correctly press the spacebar in response to a pair of eights appearing at the attended locations.
 -  To facilitate training, an additional lower-pitched tone will play whenever a pair appears, but only during the first half of the block (before the hand switch).
-- A few of the initial trials in each block will be presented at a slower pace.
 - You are encouraged to ask the experimenter any questions either now or during the practice trials.</t>
   </si>
 </sst>
